--- a/EPSS_Shipment_Data.xlsx
+++ b/EPSS_Shipment_Data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23160" windowHeight="8880" activeTab="2"/>
+    <workbookView windowWidth="23160" windowHeight="9465" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Hubs" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="258">
   <si>
     <t>HubName</t>
   </si>
@@ -744,6 +744,66 @@
   </si>
   <si>
     <t>Gguteta</t>
+  </si>
+  <si>
+    <t>teferikibru7@gmail.com</t>
+  </si>
+  <si>
+    <t>Kteferi</t>
+  </si>
+  <si>
+    <t>kalkidana671@gmail.com</t>
+  </si>
+  <si>
+    <t>Kakililu</t>
+  </si>
+  <si>
+    <t>atnasiyasheleme0@gmail.com</t>
+  </si>
+  <si>
+    <t>Asheleme</t>
+  </si>
+  <si>
+    <t>amanregea29@gmail.com</t>
+  </si>
+  <si>
+    <t>Aregea</t>
+  </si>
+  <si>
+    <t>abrhamsitotaw0@gmail.com</t>
+  </si>
+  <si>
+    <t>Asitotaw</t>
+  </si>
+  <si>
+    <t>bereketdansa@gmail.com</t>
+  </si>
+  <si>
+    <t>Bdensa</t>
+  </si>
+  <si>
+    <t>afomeendale@gmail.com</t>
+  </si>
+  <si>
+    <t>Aendale</t>
+  </si>
+  <si>
+    <t>zebirhan999@gmail.com</t>
+  </si>
+  <si>
+    <t>Zbirhan</t>
+  </si>
+  <si>
+    <t>demekekerebih27@gmail.com</t>
+  </si>
+  <si>
+    <t>Dkerebih</t>
+  </si>
+  <si>
+    <t>hilinademek26@gmail.com</t>
+  </si>
+  <si>
+    <t>Hdemeke</t>
   </si>
 </sst>
 </file>
@@ -751,10 +811,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
   </numFmts>
   <fonts count="25">
     <font>
@@ -1292,16 +1352,16 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3861,8 +3921,8 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="4" outlineLevelCol="3"/>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="29.5714285714286" customWidth="1"/>
     <col min="2" max="2" width="13.5714285714286" customWidth="1"/>
@@ -3937,6 +3997,146 @@
         <v>237</v>
       </c>
       <c r="D5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>238</v>
+      </c>
+      <c r="B6" t="s">
+        <v>229</v>
+      </c>
+      <c r="C6" t="s">
+        <v>239</v>
+      </c>
+      <c r="D6" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>240</v>
+      </c>
+      <c r="B7" t="s">
+        <v>229</v>
+      </c>
+      <c r="C7" t="s">
+        <v>241</v>
+      </c>
+      <c r="D7" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>242</v>
+      </c>
+      <c r="B8" t="s">
+        <v>229</v>
+      </c>
+      <c r="C8" t="s">
+        <v>243</v>
+      </c>
+      <c r="D8" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>244</v>
+      </c>
+      <c r="B9" t="s">
+        <v>229</v>
+      </c>
+      <c r="C9" t="s">
+        <v>245</v>
+      </c>
+      <c r="D9" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>246</v>
+      </c>
+      <c r="B10" t="s">
+        <v>229</v>
+      </c>
+      <c r="C10" t="s">
+        <v>247</v>
+      </c>
+      <c r="D10" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
+        <v>248</v>
+      </c>
+      <c r="B11" t="s">
+        <v>229</v>
+      </c>
+      <c r="C11" t="s">
+        <v>249</v>
+      </c>
+      <c r="D11" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
+        <v>250</v>
+      </c>
+      <c r="B12" t="s">
+        <v>229</v>
+      </c>
+      <c r="C12" t="s">
+        <v>251</v>
+      </c>
+      <c r="D12" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
+        <v>252</v>
+      </c>
+      <c r="B13" t="s">
+        <v>229</v>
+      </c>
+      <c r="C13" t="s">
+        <v>253</v>
+      </c>
+      <c r="D13" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
+        <v>254</v>
+      </c>
+      <c r="B14" t="s">
+        <v>229</v>
+      </c>
+      <c r="C14" t="s">
+        <v>255</v>
+      </c>
+      <c r="D14" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" t="s">
+        <v>256</v>
+      </c>
+      <c r="B15" t="s">
+        <v>229</v>
+      </c>
+      <c r="C15" t="s">
+        <v>257</v>
+      </c>
+      <c r="D15" t="s">
         <v>231</v>
       </c>
     </row>
